--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/7mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/7mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.63821745371</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>796.4255790259868</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>795.1470493221699</v>
+        <v>0.248101392</v>
+      </c>
+      <c r="Y2">
+        <v>0.262455584</v>
+      </c>
+      <c r="Z2">
+        <v>0.3611609534336716</v>
+      </c>
+      <c r="AA2">
+        <v>7.177095999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.05130531524124269</v>
+      </c>
+      <c r="AC2">
+        <v>40.8608653981175</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.63833319445</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>797.2754764134879</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>795.9453149282522</v>
+      </c>
+      <c r="X3">
+        <v>0.248068674</v>
+      </c>
+      <c r="Y3">
+        <v>0.26244699</v>
+      </c>
+      <c r="Z3">
+        <v>0.3611322328180889</v>
+      </c>
+      <c r="AA3">
+        <v>7.189157999999999</v>
+      </c>
+      <c r="AB3">
+        <v>0.05121858972920573</v>
+      </c>
+      <c r="AC3">
+        <v>40.83532552757947</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.63844951389</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>796.4184002184587</v>
       </c>
-      <c r="V4">
-        <v>0.4927739016094698</v>
-      </c>
-      <c r="W4" t="b">
+      <c r="V4" t="b">
         <v>1</v>
       </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.24807217</v>
+      </c>
+      <c r="Y4">
+        <v>0.262429798</v>
+      </c>
+      <c r="Z4">
+        <v>0.3611221405658059</v>
+      </c>
+      <c r="AA4">
+        <v>7.178814000000003</v>
+      </c>
+      <c r="AB4">
+        <v>0.0512882007694199</v>
+      </c>
+      <c r="AC4">
+        <v>40.84686680686452</v>
+      </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.63856525463</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>797.6531320854862</v>
       </c>
-      <c r="V5">
-        <v>0.632688205744772</v>
-      </c>
-      <c r="W5" t="b">
+      <c r="V5" t="b">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>40.86950072498658</v>
+      </c>
+      <c r="X5">
+        <v>0.248076616</v>
+      </c>
+      <c r="Y5">
+        <v>0.26241802</v>
+      </c>
+      <c r="Z5">
+        <v>0.3611166357656926</v>
+      </c>
+      <c r="AA5">
+        <v>7.170701999999999</v>
+      </c>
+      <c r="AB5">
+        <v>0.05134326408073055</v>
+      </c>
+      <c r="AC5">
+        <v>40.95411540548696</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.63868157408</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>795.5111692927933</v>
       </c>
-      <c r="V6">
-        <v>1.075146140548459</v>
-      </c>
-      <c r="W6" t="b">
+      <c r="V6" t="b">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>0.24805851</v>
+      </c>
+      <c r="Y6">
+        <v>0.262401148</v>
+      </c>
+      <c r="Z6">
+        <v>0.3610919368459202</v>
+      </c>
+      <c r="AA6">
+        <v>7.171319000000004</v>
+      </c>
+      <c r="AB6">
+        <v>0.05133563607817962</v>
+      </c>
+      <c r="AC6">
+        <v>40.83807188294197</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.63879789352</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>795.7248559255828</v>
       </c>
-      <c r="V7">
-        <v>1.179824530114923</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.24805184</v>
+      </c>
+      <c r="Y7">
+        <v>0.262379184</v>
+      </c>
+      <c r="Z7">
+        <v>0.3610713939429313</v>
+      </c>
+      <c r="AA7">
+        <v>7.163671999999998</v>
+      </c>
+      <c r="AB7">
+        <v>0.05138554414141097</v>
+      </c>
+      <c r="AC7">
+        <v>40.88875470858192</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.63891421296</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>795.68911482025</v>
       </c>
-      <c r="V8">
-        <v>0.1144581542062175</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.248035322</v>
+      </c>
+      <c r="Y8">
+        <v>0.26236645</v>
+      </c>
+      <c r="Z8">
+        <v>0.3610507928882669</v>
+      </c>
+      <c r="AA8">
+        <v>7.165564000000003</v>
+      </c>
+      <c r="AB8">
+        <v>0.05136967016743436</v>
+      </c>
+      <c r="AC8">
+        <v>40.87428738413405</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.6390299537</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>794.1435852822037</v>
       </c>
-      <c r="V9">
-        <v>0.9028063494087707</v>
-      </c>
-      <c r="W9" t="b">
+      <c r="V9" t="b">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>0.248028334</v>
+      </c>
+      <c r="Y9">
+        <v>0.262348624</v>
+      </c>
+      <c r="Z9">
+        <v>0.3610330386287506</v>
+      </c>
+      <c r="AA9">
+        <v>7.160145</v>
+      </c>
+      <c r="AB9">
+        <v>0.05140464319705897</v>
+      </c>
+      <c r="AC9">
+        <v>40.82266764866485</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.63914627315</v>
       </c>
@@ -1127,11 +1298,26 @@
       <c r="U10">
         <v>794.6665212900197</v>
       </c>
-      <c r="V10">
-        <v>0.7861108010657107</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
+      </c>
+      <c r="X10">
+        <v>0.248021028</v>
+      </c>
+      <c r="Y10">
+        <v>0.262320292</v>
+      </c>
+      <c r="Z10">
+        <v>0.3610074319527814</v>
+      </c>
+      <c r="AA10">
+        <v>7.149631999999997</v>
+      </c>
+      <c r="AB10">
+        <v>0.05147385811108</v>
+      </c>
+      <c r="AC10">
+        <v>40.90455176250801</v>
       </c>
     </row>
   </sheetData>
